--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/pre LAM_HRM-2031-0172/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/pre LAM_HRM-2031-0172/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.66069</v>
+        <v>16.91864</v>
       </c>
       <c r="D2" t="n">
-        <v>17.16346</v>
+        <v>16.76916</v>
       </c>
       <c r="E2" t="n">
-        <v>16.83309</v>
+        <v>16.84555</v>
       </c>
       <c r="F2" t="n">
-        <v>42.52252</v>
+        <v>42.83157</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05049</v>
+        <v>0.0505</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82072</v>
+        <v>1.81721</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.35731</v>
+        <v>17.29109</v>
       </c>
       <c r="D3" t="n">
-        <v>16.78718</v>
+        <v>16.89893</v>
       </c>
       <c r="E3" t="n">
-        <v>16.70049</v>
+        <v>16.93459</v>
       </c>
       <c r="F3" t="n">
-        <v>42.72613</v>
+        <v>43.86659</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05059</v>
+        <v>0.05166</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8438</v>
+        <v>1.85343</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.84878</v>
+        <v>17.09325</v>
       </c>
       <c r="D4" t="n">
-        <v>16.34177</v>
+        <v>16.61651</v>
       </c>
       <c r="E4" t="n">
-        <v>17.05911</v>
+        <v>16.92315</v>
       </c>
       <c r="F4" t="n">
-        <v>42.32881</v>
+        <v>43.07213</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05064</v>
+        <v>0.05197</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82091</v>
+        <v>1.86921</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.61344</v>
+        <v>16.7294</v>
       </c>
       <c r="D6" t="n">
-        <v>16.23412</v>
+        <v>16.15139</v>
       </c>
       <c r="E6" t="n">
-        <v>16.68361</v>
+        <v>16.2549</v>
       </c>
       <c r="F6" t="n">
-        <v>21.96886</v>
+        <v>22.24503</v>
       </c>
       <c r="G6" t="n">
-        <v>34.47991</v>
+        <v>34.8538</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.72939</v>
+        <v>16.99804</v>
       </c>
       <c r="D7" t="n">
-        <v>16.3339</v>
+        <v>15.76188</v>
       </c>
       <c r="E7" t="n">
-        <v>16.757</v>
+        <v>16.63346</v>
       </c>
       <c r="F7" t="n">
-        <v>21.73071</v>
+        <v>21.52508</v>
       </c>
       <c r="G7" t="n">
-        <v>34.09574</v>
+        <v>34.38985</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.63843</v>
+        <v>16.96118</v>
       </c>
       <c r="D8" t="n">
-        <v>15.97054</v>
+        <v>16.12565</v>
       </c>
       <c r="E8" t="n">
-        <v>16.7816</v>
+        <v>16.85654</v>
       </c>
       <c r="F8" t="n">
-        <v>22.00958</v>
+        <v>22.06975</v>
       </c>
       <c r="G8" t="n">
-        <v>34.34378</v>
+        <v>34.08105</v>
       </c>
     </row>
   </sheetData>
